--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2020_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2020_los_lagos.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:13</t>
+    <t xml:space="preserve">2026-09-24 01:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -681,13 +681,13 @@
         <v>30</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="9">
@@ -704,13 +704,13 @@
         <v>30</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="10">
@@ -730,10 +730,10 @@
         <v>-0.08</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="11">
@@ -750,10 +750,10 @@
         <v>30</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>0.57</v>
@@ -796,13 +796,13 @@
         <v>30</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="14">
@@ -819,13 +819,13 @@
         <v>30</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="15">
@@ -845,7 +845,7 @@
         <v>-0.01</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>-0.08</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2020_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2020_los_lagos.xlsx
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:03</t>
+    <t xml:space="preserve">2026-10-01 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2020_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_rezjov_a_2020_los_lagos.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:13</t>
+    <t xml:space="preserve">2026-10-05 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
